--- a/masters/master_town_village.xlsx
+++ b/masters/master_town_village.xlsx
@@ -795,8 +795,12 @@
           <t>BARAKANI</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>-12.13923932658967</v>
+      </c>
+      <c r="H11" t="n">
+        <v>44.43117532297685</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1266,10 +1270,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-12.3491749</v>
+        <v>-12.3201731</v>
       </c>
       <c r="H24" t="n">
-        <v>43.8222246</v>
+        <v>44.4731801</v>
       </c>
     </row>
     <row r="25">
@@ -2079,8 +2083,12 @@
           <t>BARAKANI</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>-12.13923932658967</v>
+      </c>
+      <c r="H47" t="n">
+        <v>44.43117532297685</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3358,10 +3366,10 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>-12.3491749</v>
+        <v>-12.3201731</v>
       </c>
       <c r="H82" t="n">
-        <v>43.8222246</v>
+        <v>44.4731801</v>
       </c>
     </row>
     <row r="83">
@@ -4233,8 +4241,12 @@
           <t>MILEMBENI</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="G106" t="n">
+        <v>-12.20224155888374</v>
+      </c>
+      <c r="H106" t="n">
+        <v>44.26310520358714</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7921,7 +7933,7 @@
         <v>-11.88428639896506</v>
       </c>
       <c r="H206" t="n">
-        <v>43.49101856641398</v>
+        <v>43.49101856641399</v>
       </c>
     </row>
     <row r="207">
@@ -12767,8 +12779,12 @@
           <t>MILEMBENI</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
+      <c r="G337" t="n">
+        <v>-12.20224155888374</v>
+      </c>
+      <c r="H337" t="n">
+        <v>44.26310520358714</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">

--- a/masters/master_town_village.xlsx
+++ b/masters/master_town_village.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$334</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -415,6 +417,16 @@
   </sheetPr>
   <dimension ref="A1:H334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -489,8 +501,6 @@
           <t>FOMBONI</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,8 +533,6 @@
           <t>MBOIGOMA</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,8 +565,6 @@
           <t>BANDAR SALAMA</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -591,8 +597,6 @@
           <t>DJOIEZI</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,8 +629,6 @@
           <t>M'BATSE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -659,8 +661,6 @@
           <t>HOANI</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -693,8 +693,6 @@
           <t>DOMONI</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -727,8 +725,6 @@
           <t>HAMBA</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -761,8 +757,6 @@
           <t>BARAKANI</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -947,8 +941,6 @@
           <t>MIREMANI</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -981,8 +973,6 @@
           <t>NDRONDRONI</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1053,8 +1043,6 @@
           <t>NDREMEANI</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1087,8 +1075,6 @@
           <t>ZIROUDANI</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1159,8 +1145,6 @@
           <t>MLANBANDA</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1269,8 +1253,6 @@
           <t>HAGNAMOIDA</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1379,8 +1361,6 @@
           <t>MUTSAMUDU</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1451,8 +1431,6 @@
           <t>MWAMWA I</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1485,8 +1463,6 @@
           <t>MWAMWA II</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1519,8 +1495,6 @@
           <t>CHICONI1</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1553,8 +1527,6 @@
           <t>MIRONTSI</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1587,8 +1559,6 @@
           <t>MDJIMANDRA</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1697,8 +1667,6 @@
           <t>MAWENI</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1731,8 +1699,6 @@
           <t>CHICONI 2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1765,8 +1731,6 @@
           <t>MPOUZINI</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1837,8 +1801,6 @@
           <t>BANDRANI MTSANGANI</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1871,8 +1833,6 @@
           <t>CHITROUNI</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1943,8 +1903,6 @@
           <t>MDJAMAOUE</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1977,8 +1935,6 @@
           <t>OUANI</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2011,8 +1967,6 @@
           <t>BARAKANI</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2159,8 +2113,6 @@
           <t>BAZIMINI</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2269,8 +2221,6 @@
           <t>TSEMBEHOU</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2379,8 +2329,6 @@
           <t>DOMONI</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2451,8 +2399,6 @@
           <t>BWELADUGU</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2485,8 +2431,6 @@
           <t>NGADZALE</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2671,8 +2615,6 @@
           <t>KONI DJODJO</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2819,8 +2761,6 @@
           <t>BAMBAO MTSANGA</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2853,8 +2793,6 @@
           <t>MROMAJI</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2925,8 +2863,6 @@
           <t>MAHALE</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2959,8 +2895,6 @@
           <t>HAREMBO I</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3107,8 +3041,6 @@
           <t>ADDA DAWENI</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3293,8 +3225,6 @@
           <t>MREMANI</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3327,8 +3257,6 @@
           <t>BANDA KOUNI</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3437,8 +3365,6 @@
           <t>ONGODJOU</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3585,8 +3511,6 @@
           <t>TRINDRINI</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,8 +3543,6 @@
           <t>SHAWENI</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3805,8 +3727,6 @@
           <t>MRAMANI</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3839,8 +3759,6 @@
           <t>HANTSAHII</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3873,8 +3791,6 @@
           <t>NYAMBOIMRO</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,8 +3823,6 @@
           <t>DZIANII</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4131,8 +4045,6 @@
           <t>MILEMBENI</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4203,8 +4115,6 @@
           <t>MROMOUHOULI</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4275,8 +4185,6 @@
           <t>HASSIMPAO</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4727,8 +4635,6 @@
           <t>IMERE YA GAWANI</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4761,8 +4667,6 @@
           <t>MOYA</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4947,8 +4851,6 @@
           <t>MAWENI</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4981,8 +4883,6 @@
           <t>MORONI</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5015,8 +4915,6 @@
           <t>MKAZI</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5125,8 +5023,6 @@
           <t>VOUVOUNI</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5235,8 +5131,6 @@
           <t>NIOUMADZAHA</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5269,8 +5163,6 @@
           <t>MOIDZAZA DJOUMBE</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5341,8 +5233,6 @@
           <t>DAOUENI</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5451,8 +5341,6 @@
           <t>BOENI YA BAMBAO</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5485,8 +5373,6 @@
           <t>ICONI</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5519,8 +5405,6 @@
           <t>MBACHILE</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5667,8 +5551,6 @@
           <t>MITSOUDJE</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5701,8 +5583,6 @@
           <t>TROUMBENI</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5849,8 +5729,6 @@
           <t>NKOMIONI</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5921,8 +5799,6 @@
           <t>SINGANI</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6107,8 +5983,6 @@
           <t>DEMBENI</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6521,8 +6395,6 @@
           <t>OUZIOINI</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6555,8 +6427,6 @@
           <t>IFOUNDIHE CHADJOU</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6703,8 +6573,6 @@
           <t>DOMONI</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6813,8 +6681,6 @@
           <t>FOUMBOUNI</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7227,8 +7093,6 @@
           <t>BANDAMADJI LADOMBA</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7451,8 +7315,6 @@
           <t>SIMBOUSSA YA MBADJINI</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7523,8 +7385,6 @@
           <t>NGNAMBENI</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7823,8 +7683,6 @@
           <t>KOIMBANI YA WACHILI</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7857,8 +7715,6 @@
           <t>IROHE</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8005,8 +7861,6 @@
           <t>SADANI</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8191,8 +8045,6 @@
           <t>ITSINKOUDI</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8453,8 +8305,6 @@
           <t>MTSANGADJOU</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8563,8 +8413,6 @@
           <t>MIDJINDZE</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8597,8 +8445,6 @@
           <t>MADJOMA</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8897,8 +8743,6 @@
           <t>MBENI</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9007,8 +8851,6 @@
           <t>SADA CHIHOUWE</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9041,8 +8883,6 @@
           <t>SADA MHUWAMBOI</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9189,8 +9029,6 @@
           <t>KOURANI YA HAMAHAMET</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9299,8 +9137,6 @@
           <t>DIMADJOU YA HAMAHAMET</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9447,8 +9283,6 @@
           <t>BAMBADJANI</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9671,8 +9505,6 @@
           <t>MADJEOUENI</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9705,8 +9537,6 @@
           <t>SADANI YA MBOIKOU</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9967,8 +9797,6 @@
           <t>BANGOIKOUNI</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10115,8 +9943,6 @@
           <t>OUEMANI</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -10263,8 +10089,6 @@
           <t>MEMBOI - BOINI</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10297,8 +10121,6 @@
           <t>HADAWA</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10407,8 +10229,6 @@
           <t>NKOURANI YA MITSAMIHOULI</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10479,8 +10299,6 @@
           <t>BANGOI MAFUSA NKOA</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10703,8 +10521,6 @@
           <t>NTSADJENI</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10813,8 +10629,6 @@
           <t>DJOMANI</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10885,8 +10699,6 @@
           <t>VOUVOUNI YA MBOUNDE</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11147,8 +10959,6 @@
           <t>NTSAOUENI</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -11485,8 +11295,6 @@
           <t>HAHAYA</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11595,8 +11403,6 @@
           <t>MBALENI</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11667,8 +11473,6 @@
           <t>MBANGANI</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11815,8 +11619,6 @@
           <t>BATSA ITSANDRA</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12039,8 +11841,6 @@
           <t>ITSANDRA MDJINI</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -12339,8 +12139,6 @@
           <t>DZAHANI II</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12525,8 +12323,6 @@
           <t>NTSOUDJINI</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12597,8 +12393,6 @@
           <t>MILEMBENI</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12669,10 +12463,9 @@
           <t>ZIVANDANI</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H334"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/masters/master_town_village.xlsx
+++ b/masters/master_town_village.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1859" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="729">
   <si>
     <t>country_id</t>
   </si>
@@ -55,6 +55,9 @@
     <t>KM32</t>
   </si>
   <si>
+    <t>KM33</t>
+  </si>
+  <si>
     <t>KM31</t>
   </si>
   <si>
@@ -67,9 +70,15 @@
     <t>KM11</t>
   </si>
   <si>
+    <t>KM12</t>
+  </si>
+  <si>
     <t>KM15</t>
   </si>
   <si>
+    <t>KM16</t>
+  </si>
+  <si>
     <t>KM27</t>
   </si>
   <si>
@@ -88,6 +97,9 @@
     <t>KM21</t>
   </si>
   <si>
+    <t>KM26</t>
+  </si>
+  <si>
     <t>KM23</t>
   </si>
   <si>
@@ -97,9 +109,15 @@
     <t>KM322</t>
   </si>
   <si>
+    <t>KM323</t>
+  </si>
+  <si>
     <t>KM332</t>
   </si>
   <si>
+    <t>KM331</t>
+  </si>
+  <si>
     <t>KM311</t>
   </si>
   <si>
@@ -112,6 +130,9 @@
     <t>KM131</t>
   </si>
   <si>
+    <t>KM132</t>
+  </si>
+  <si>
     <t>KM143</t>
   </si>
   <si>
@@ -124,15 +145,30 @@
     <t>KM112</t>
   </si>
   <si>
+    <t>KM115</t>
+  </si>
+  <si>
     <t>KM114</t>
   </si>
   <si>
+    <t>KM111</t>
+  </si>
+  <si>
+    <t>KM113</t>
+  </si>
+  <si>
     <t>KM121</t>
   </si>
   <si>
+    <t>KM124</t>
+  </si>
+  <si>
     <t>KM125</t>
   </si>
   <si>
+    <t>KM122</t>
+  </si>
+  <si>
     <t>KM123</t>
   </si>
   <si>
@@ -148,6 +184,9 @@
     <t>KM274</t>
   </si>
   <si>
+    <t>KM273</t>
+  </si>
+  <si>
     <t>KM271</t>
   </si>
   <si>
@@ -178,6 +217,9 @@
     <t>KM282</t>
   </si>
   <si>
+    <t>KM283</t>
+  </si>
+  <si>
     <t>KM281</t>
   </si>
   <si>
@@ -190,6 +232,9 @@
     <t>KM211</t>
   </si>
   <si>
+    <t>KM261</t>
+  </si>
+  <si>
     <t>KM262</t>
   </si>
   <si>
@@ -232,6 +277,18 @@
     <t>KM322_0003</t>
   </si>
   <si>
+    <t>KM323_0001</t>
+  </si>
+  <si>
+    <t>KM323_0002</t>
+  </si>
+  <si>
+    <t>KM323_0003</t>
+  </si>
+  <si>
+    <t>KM323_0004</t>
+  </si>
+  <si>
     <t>KM332_0001</t>
   </si>
   <si>
@@ -250,6 +307,18 @@
     <t>KM332_0006</t>
   </si>
   <si>
+    <t>KM331_0001</t>
+  </si>
+  <si>
+    <t>KM331_0002</t>
+  </si>
+  <si>
+    <t>KM331_0003</t>
+  </si>
+  <si>
+    <t>KM331_0004</t>
+  </si>
+  <si>
     <t>KM311_0001</t>
   </si>
   <si>
@@ -316,6 +385,18 @@
     <t>KM131_0008</t>
   </si>
   <si>
+    <t>KM132_0001</t>
+  </si>
+  <si>
+    <t>KM132_0002</t>
+  </si>
+  <si>
+    <t>KM132_0003</t>
+  </si>
+  <si>
+    <t>KM132_0004</t>
+  </si>
+  <si>
     <t>KM143_0001</t>
   </si>
   <si>
@@ -361,6 +442,21 @@
     <t>KM112_0004</t>
   </si>
   <si>
+    <t>KM115_0001</t>
+  </si>
+  <si>
+    <t>KM115_0002</t>
+  </si>
+  <si>
+    <t>KM115_0003</t>
+  </si>
+  <si>
+    <t>KM115_0004</t>
+  </si>
+  <si>
+    <t>KM115_0005</t>
+  </si>
+  <si>
     <t>KM114_0001</t>
   </si>
   <si>
@@ -373,6 +469,30 @@
     <t>KM114_0004</t>
   </si>
   <si>
+    <t>KM111_0001</t>
+  </si>
+  <si>
+    <t>KM111_0002</t>
+  </si>
+  <si>
+    <t>KM111_0003</t>
+  </si>
+  <si>
+    <t>KM111_0004</t>
+  </si>
+  <si>
+    <t>KM113_0001</t>
+  </si>
+  <si>
+    <t>KM113_0002</t>
+  </si>
+  <si>
+    <t>KM113_0003</t>
+  </si>
+  <si>
+    <t>KM113_0004</t>
+  </si>
+  <si>
     <t>KM121_0001</t>
   </si>
   <si>
@@ -388,6 +508,18 @@
     <t>KM121_0005</t>
   </si>
   <si>
+    <t>KM124_0001</t>
+  </si>
+  <si>
+    <t>KM124_0002</t>
+  </si>
+  <si>
+    <t>KM124_0003</t>
+  </si>
+  <si>
+    <t>KM124_0004</t>
+  </si>
+  <si>
     <t>KM125_0001</t>
   </si>
   <si>
@@ -403,6 +535,21 @@
     <t>KM125_0005</t>
   </si>
   <si>
+    <t>KM122_0001</t>
+  </si>
+  <si>
+    <t>KM122_0002</t>
+  </si>
+  <si>
+    <t>KM122_0003</t>
+  </si>
+  <si>
+    <t>KM122_0004</t>
+  </si>
+  <si>
+    <t>KM122_0005</t>
+  </si>
+  <si>
     <t>KM123_0001</t>
   </si>
   <si>
@@ -505,6 +652,15 @@
     <t>KM274_0001</t>
   </si>
   <si>
+    <t>KM273_0001</t>
+  </si>
+  <si>
+    <t>KM273_0002</t>
+  </si>
+  <si>
+    <t>KM273_0003</t>
+  </si>
+  <si>
     <t>KM271_0001</t>
   </si>
   <si>
@@ -757,6 +913,27 @@
     <t>KM282_0010</t>
   </si>
   <si>
+    <t>KM283_0001</t>
+  </si>
+  <si>
+    <t>KM283_0002</t>
+  </si>
+  <si>
+    <t>KM283_0003</t>
+  </si>
+  <si>
+    <t>KM283_0004</t>
+  </si>
+  <si>
+    <t>KM283_0005</t>
+  </si>
+  <si>
+    <t>KM283_0006</t>
+  </si>
+  <si>
+    <t>KM283_0007</t>
+  </si>
+  <si>
     <t>KM281_0001</t>
   </si>
   <si>
@@ -878,6 +1055,18 @@
   </si>
   <si>
     <t>KM211_0008</t>
+  </si>
+  <si>
+    <t>KM261_0001</t>
+  </si>
+  <si>
+    <t>KM261_0002</t>
+  </si>
+  <si>
+    <t>KM261_0003</t>
+  </si>
+  <si>
+    <t>KM261_0004</t>
   </si>
   <si>
     <t>KM262_0001</t>
@@ -2409,13 +2598,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>358</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2429,13 +2618,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>359</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2449,13 +2638,13 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>360</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2469,13 +2658,13 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>361</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2488,8 +2677,14 @@
       <c r="C6" t="s">
         <v>12</v>
       </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
       <c r="F6" t="s">
-        <v>362</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2502,8 +2697,14 @@
       <c r="C7" t="s">
         <v>12</v>
       </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
       <c r="F7" t="s">
-        <v>363</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2516,8 +2717,14 @@
       <c r="C8" t="s">
         <v>12</v>
       </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
       <c r="F8" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2530,8 +2737,14 @@
       <c r="C9" t="s">
         <v>12</v>
       </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
       <c r="F9" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2541,14 +2754,17 @@
       <c r="B10" t="s">
         <v>9</v>
       </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>365</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2558,14 +2774,17 @@
       <c r="B11" t="s">
         <v>9</v>
       </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>366</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2575,14 +2794,17 @@
       <c r="B12" t="s">
         <v>9</v>
       </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F12" t="s">
-        <v>366</v>
+        <v>429</v>
       </c>
       <c r="G12">
         <v>-12.13923932658967</v>
@@ -2598,14 +2820,17 @@
       <c r="B13" t="s">
         <v>9</v>
       </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>367</v>
+        <v>430</v>
       </c>
       <c r="G13">
         <v>-12.30256921447786</v>
@@ -2621,14 +2846,17 @@
       <c r="B14" t="s">
         <v>9</v>
       </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="G14">
         <v>-12.32646849061358</v>
@@ -2644,14 +2872,17 @@
       <c r="B15" t="s">
         <v>9</v>
       </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>369</v>
+        <v>432</v>
       </c>
       <c r="G15">
         <v>-12.34693056281361</v>
@@ -2667,8 +2898,17 @@
       <c r="B16" t="s">
         <v>9</v>
       </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" t="s">
+        <v>97</v>
+      </c>
       <c r="F16" t="s">
-        <v>370</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2678,8 +2918,17 @@
       <c r="B17" t="s">
         <v>9</v>
       </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
       <c r="F17" t="s">
-        <v>371</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2689,8 +2938,17 @@
       <c r="B18" t="s">
         <v>9</v>
       </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
       <c r="F18" t="s">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="G18">
         <v>-12.36716328241932</v>
@@ -2706,8 +2964,17 @@
       <c r="B19" t="s">
         <v>9</v>
       </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" t="s">
+        <v>100</v>
+      </c>
       <c r="F19" t="s">
-        <v>373</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2718,16 +2985,16 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>374</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2738,16 +3005,16 @@
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>375</v>
+        <v>438</v>
       </c>
       <c r="G21">
         <v>-12.345524</v>
@@ -2764,16 +3031,16 @@
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>376</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2784,16 +3051,16 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>377</v>
+        <v>440</v>
       </c>
       <c r="G23">
         <v>-12.3201731</v>
@@ -2810,16 +3077,16 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s">
-        <v>377</v>
+        <v>440</v>
       </c>
       <c r="G24">
         <v>-12.3491749</v>
@@ -2836,16 +3103,16 @@
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>378</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2856,16 +3123,16 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="G26">
         <v>-12.3699484</v>
@@ -2882,16 +3149,16 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>380</v>
+        <v>443</v>
       </c>
       <c r="G27">
         <v>-12.3782942</v>
@@ -2908,16 +3175,16 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>381</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2928,16 +3195,16 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
-        <v>382</v>
+        <v>445</v>
       </c>
       <c r="G29">
         <v>-12.17696514995421</v>
@@ -2954,16 +3221,16 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>383</v>
+        <v>446</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2974,16 +3241,16 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>384</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2994,16 +3261,16 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3014,16 +3281,16 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3034,16 +3301,16 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>387</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3054,16 +3321,16 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>388</v>
+        <v>451</v>
       </c>
       <c r="G35">
         <v>-12.1961321</v>
@@ -3080,16 +3347,16 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>389</v>
+        <v>452</v>
       </c>
       <c r="G36">
         <v>-12.19439924271254</v>
@@ -3106,16 +3373,16 @@
         <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F37" t="s">
-        <v>390</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3126,16 +3393,16 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="F38" t="s">
-        <v>390</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3146,16 +3413,16 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>391</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3166,16 +3433,16 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="F40" t="s">
-        <v>392</v>
+        <v>455</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3186,16 +3453,16 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E41" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="G41">
         <v>-12.15953586452051</v>
@@ -3212,10 +3479,16 @@
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" t="s">
+        <v>123</v>
       </c>
       <c r="F42" t="s">
-        <v>394</v>
+        <v>457</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3226,10 +3499,16 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" t="s">
+        <v>124</v>
       </c>
       <c r="F43" t="s">
-        <v>395</v>
+        <v>458</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -3240,10 +3519,16 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" t="s">
+        <v>125</v>
       </c>
       <c r="F44" t="s">
-        <v>396</v>
+        <v>459</v>
       </c>
       <c r="G44">
         <v>-12.1914952</v>
@@ -3260,10 +3545,16 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" t="s">
+        <v>126</v>
       </c>
       <c r="F45" t="s">
-        <v>397</v>
+        <v>460</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -3274,16 +3565,16 @@
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>398</v>
+        <v>461</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3294,16 +3585,16 @@
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="F47" t="s">
-        <v>366</v>
+        <v>429</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -3314,16 +3605,16 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F48" t="s">
-        <v>366</v>
+        <v>429</v>
       </c>
       <c r="G48">
         <v>-12.13923932658967</v>
@@ -3340,16 +3631,16 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="F49" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="G49">
         <v>-12.13867825534638</v>
@@ -3366,16 +3657,16 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="F50" t="s">
-        <v>400</v>
+        <v>463</v>
       </c>
       <c r="G50">
         <v>-12.14566237444104</v>
@@ -3392,16 +3683,16 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E51" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F51" t="s">
-        <v>401</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -3412,16 +3703,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E52" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="F52" t="s">
-        <v>402</v>
+        <v>465</v>
       </c>
       <c r="G52">
         <v>-12.1599178</v>
@@ -3438,16 +3729,16 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="F53" t="s">
-        <v>403</v>
+        <v>466</v>
       </c>
       <c r="G53">
         <v>-12.1735498</v>
@@ -3464,16 +3755,16 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E54" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="F54" t="s">
-        <v>404</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -3484,16 +3775,16 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E55" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="F55" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="G55">
         <v>-12.2145867</v>
@@ -3510,16 +3801,16 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E56" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="F56" t="s">
-        <v>406</v>
+        <v>469</v>
       </c>
       <c r="G56">
         <v>-12.1998655</v>
@@ -3536,16 +3827,16 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="F57" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -3556,16 +3847,16 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E58" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="F58" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3576,16 +3867,16 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="F59" t="s">
-        <v>407</v>
+        <v>470</v>
       </c>
       <c r="G59">
         <v>-12.2444788</v>
@@ -3602,16 +3893,16 @@
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="F60" t="s">
-        <v>408</v>
+        <v>471</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -3622,10 +3913,16 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" t="s">
+        <v>142</v>
       </c>
       <c r="F61" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -3636,10 +3933,16 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" t="s">
+        <v>143</v>
       </c>
       <c r="F62" t="s">
-        <v>410</v>
+        <v>473</v>
       </c>
       <c r="G62">
         <v>-12.28260579088212</v>
@@ -3656,10 +3959,16 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D63" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" t="s">
+        <v>144</v>
       </c>
       <c r="F63" t="s">
-        <v>411</v>
+        <v>474</v>
       </c>
       <c r="G63">
         <v>-12.27236795835944</v>
@@ -3676,10 +3985,16 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" t="s">
+        <v>145</v>
       </c>
       <c r="F64" t="s">
-        <v>411</v>
+        <v>474</v>
       </c>
       <c r="G64">
         <v>-12.23801036263309</v>
@@ -3696,10 +4011,16 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
+        <v>43</v>
+      </c>
+      <c r="E65" t="s">
+        <v>146</v>
       </c>
       <c r="F65" t="s">
-        <v>412</v>
+        <v>475</v>
       </c>
       <c r="G65">
         <v>-12.27104021977427</v>
@@ -3716,16 +4037,16 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E66" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="F66" t="s">
-        <v>413</v>
+        <v>476</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -3736,16 +4057,16 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E67" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="F67" t="s">
-        <v>414</v>
+        <v>477</v>
       </c>
       <c r="G67">
         <v>-12.21994053589582</v>
@@ -3762,16 +4083,16 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E68" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="F68" t="s">
-        <v>415</v>
+        <v>478</v>
       </c>
       <c r="G68">
         <v>-12.22434930494048</v>
@@ -3788,16 +4109,16 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E69" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="F69" t="s">
-        <v>416</v>
+        <v>479</v>
       </c>
       <c r="G69">
         <v>-12.22780501790426</v>
@@ -3814,10 +4135,16 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" t="s">
+        <v>151</v>
       </c>
       <c r="F70" t="s">
-        <v>417</v>
+        <v>480</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3828,10 +4155,16 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
+        <v>45</v>
+      </c>
+      <c r="E71" t="s">
+        <v>152</v>
       </c>
       <c r="F71" t="s">
-        <v>418</v>
+        <v>481</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3842,10 +4175,16 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
+        <v>45</v>
+      </c>
+      <c r="E72" t="s">
+        <v>153</v>
       </c>
       <c r="F72" t="s">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="G72">
         <v>-12.1738084</v>
@@ -3862,10 +4201,16 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
+        <v>45</v>
+      </c>
+      <c r="E73" t="s">
+        <v>154</v>
       </c>
       <c r="F73" t="s">
-        <v>420</v>
+        <v>483</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3876,10 +4221,16 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D74" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" t="s">
+        <v>155</v>
       </c>
       <c r="F74" t="s">
-        <v>421</v>
+        <v>484</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3890,10 +4241,16 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75" t="s">
+        <v>156</v>
       </c>
       <c r="F75" t="s">
-        <v>422</v>
+        <v>485</v>
       </c>
       <c r="G75">
         <v>-12.1504381399188</v>
@@ -3910,10 +4267,16 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
+        <v>46</v>
+      </c>
+      <c r="E76" t="s">
+        <v>157</v>
       </c>
       <c r="F76" t="s">
-        <v>423</v>
+        <v>486</v>
       </c>
       <c r="G76">
         <v>-12.12283410219443</v>
@@ -3930,10 +4293,16 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D77" t="s">
+        <v>46</v>
+      </c>
+      <c r="E77" t="s">
+        <v>158</v>
       </c>
       <c r="F77" t="s">
-        <v>424</v>
+        <v>487</v>
       </c>
       <c r="G77">
         <v>-12.097363785809</v>
@@ -3949,14 +4318,17 @@
       <c r="B78" t="s">
         <v>10</v>
       </c>
+      <c r="C78" t="s">
+        <v>18</v>
+      </c>
       <c r="D78" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E78" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="F78" t="s">
-        <v>425</v>
+        <v>488</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3966,14 +4338,17 @@
       <c r="B79" t="s">
         <v>10</v>
       </c>
+      <c r="C79" t="s">
+        <v>18</v>
+      </c>
       <c r="D79" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E79" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F79" t="s">
-        <v>426</v>
+        <v>489</v>
       </c>
       <c r="G79">
         <v>-12.2974902</v>
@@ -3989,14 +4364,17 @@
       <c r="B80" t="s">
         <v>10</v>
       </c>
+      <c r="C80" t="s">
+        <v>18</v>
+      </c>
       <c r="D80" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E80" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F80" t="s">
-        <v>427</v>
+        <v>490</v>
       </c>
       <c r="G80">
         <v>-12.2982131</v>
@@ -4012,14 +4390,17 @@
       <c r="B81" t="s">
         <v>10</v>
       </c>
+      <c r="C81" t="s">
+        <v>18</v>
+      </c>
       <c r="D81" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E81" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="F81" t="s">
-        <v>377</v>
+        <v>440</v>
       </c>
       <c r="G81">
         <v>-12.3201731</v>
@@ -4035,14 +4416,17 @@
       <c r="B82" t="s">
         <v>10</v>
       </c>
+      <c r="C82" t="s">
+        <v>18</v>
+      </c>
       <c r="D82" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E82" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="F82" t="s">
-        <v>377</v>
+        <v>440</v>
       </c>
       <c r="G82">
         <v>-12.3491749</v>
@@ -4058,8 +4442,17 @@
       <c r="B83" t="s">
         <v>10</v>
       </c>
+      <c r="C83" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" t="s">
+        <v>164</v>
+      </c>
       <c r="F83" t="s">
-        <v>428</v>
+        <v>491</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -4069,8 +4462,17 @@
       <c r="B84" t="s">
         <v>10</v>
       </c>
+      <c r="C84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" t="s">
+        <v>48</v>
+      </c>
+      <c r="E84" t="s">
+        <v>165</v>
+      </c>
       <c r="F84" t="s">
-        <v>429</v>
+        <v>492</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -4080,8 +4482,17 @@
       <c r="B85" t="s">
         <v>10</v>
       </c>
+      <c r="C85" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" t="s">
+        <v>48</v>
+      </c>
+      <c r="E85" t="s">
+        <v>166</v>
+      </c>
       <c r="F85" t="s">
-        <v>430</v>
+        <v>493</v>
       </c>
       <c r="G85">
         <v>-12.33363960096466</v>
@@ -4097,8 +4508,17 @@
       <c r="B86" t="s">
         <v>10</v>
       </c>
+      <c r="C86" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" t="s">
+        <v>48</v>
+      </c>
+      <c r="E86" t="s">
+        <v>167</v>
+      </c>
       <c r="F86" t="s">
-        <v>431</v>
+        <v>494</v>
       </c>
       <c r="G86">
         <v>-12.33024366437102</v>
@@ -4114,14 +4534,17 @@
       <c r="B87" t="s">
         <v>10</v>
       </c>
+      <c r="C87" t="s">
+        <v>18</v>
+      </c>
       <c r="D87" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E87" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="F87" t="s">
-        <v>432</v>
+        <v>495</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -4131,14 +4554,17 @@
       <c r="B88" t="s">
         <v>10</v>
       </c>
+      <c r="C88" t="s">
+        <v>18</v>
+      </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E88" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="F88" t="s">
-        <v>433</v>
+        <v>496</v>
       </c>
       <c r="G88">
         <v>-12.33551667432872</v>
@@ -4154,14 +4580,17 @@
       <c r="B89" t="s">
         <v>10</v>
       </c>
+      <c r="C89" t="s">
+        <v>18</v>
+      </c>
       <c r="D89" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E89" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="F89" t="s">
-        <v>434</v>
+        <v>497</v>
       </c>
       <c r="G89">
         <v>-12.32541872238746</v>
@@ -4177,14 +4606,17 @@
       <c r="B90" t="s">
         <v>10</v>
       </c>
+      <c r="C90" t="s">
+        <v>18</v>
+      </c>
       <c r="D90" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E90" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="F90" t="s">
-        <v>435</v>
+        <v>498</v>
       </c>
       <c r="G90">
         <v>-12.32415361558692</v>
@@ -4200,14 +4632,17 @@
       <c r="B91" t="s">
         <v>10</v>
       </c>
+      <c r="C91" t="s">
+        <v>18</v>
+      </c>
       <c r="D91" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E91" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="F91" t="s">
-        <v>436</v>
+        <v>499</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -4217,8 +4652,17 @@
       <c r="B92" t="s">
         <v>10</v>
       </c>
+      <c r="C92" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" t="s">
+        <v>50</v>
+      </c>
+      <c r="E92" t="s">
+        <v>173</v>
+      </c>
       <c r="F92" t="s">
-        <v>437</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -4228,8 +4672,17 @@
       <c r="B93" t="s">
         <v>10</v>
       </c>
+      <c r="C93" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" t="s">
+        <v>50</v>
+      </c>
+      <c r="E93" t="s">
+        <v>174</v>
+      </c>
       <c r="F93" t="s">
-        <v>438</v>
+        <v>501</v>
       </c>
       <c r="G93">
         <v>-12.3743914</v>
@@ -4245,8 +4698,17 @@
       <c r="B94" t="s">
         <v>10</v>
       </c>
+      <c r="C94" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" t="s">
+        <v>50</v>
+      </c>
+      <c r="E94" t="s">
+        <v>175</v>
+      </c>
       <c r="F94" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="G94">
         <v>-12.3728211</v>
@@ -4262,8 +4724,17 @@
       <c r="B95" t="s">
         <v>10</v>
       </c>
+      <c r="C95" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" t="s">
+        <v>176</v>
+      </c>
       <c r="F95" t="s">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="G95">
         <v>-12.3479406</v>
@@ -4279,8 +4750,17 @@
       <c r="B96" t="s">
         <v>10</v>
       </c>
+      <c r="C96" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" t="s">
+        <v>50</v>
+      </c>
+      <c r="E96" t="s">
+        <v>177</v>
+      </c>
       <c r="F96" t="s">
-        <v>441</v>
+        <v>504</v>
       </c>
       <c r="G96">
         <v>-12.345461</v>
@@ -4296,14 +4776,17 @@
       <c r="B97" t="s">
         <v>10</v>
       </c>
+      <c r="C97" t="s">
+        <v>18</v>
+      </c>
       <c r="D97" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E97" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="F97" t="s">
-        <v>442</v>
+        <v>505</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -4313,14 +4796,17 @@
       <c r="B98" t="s">
         <v>10</v>
       </c>
+      <c r="C98" t="s">
+        <v>18</v>
+      </c>
       <c r="D98" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E98" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="F98" t="s">
-        <v>443</v>
+        <v>506</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -4330,14 +4816,17 @@
       <c r="B99" t="s">
         <v>10</v>
       </c>
+      <c r="C99" t="s">
+        <v>18</v>
+      </c>
       <c r="D99" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E99" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="F99" t="s">
-        <v>444</v>
+        <v>507</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4347,14 +4836,17 @@
       <c r="B100" t="s">
         <v>10</v>
       </c>
+      <c r="C100" t="s">
+        <v>18</v>
+      </c>
       <c r="D100" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E100" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="F100" t="s">
-        <v>445</v>
+        <v>508</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -4365,16 +4857,16 @@
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E101" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="F101" t="s">
-        <v>446</v>
+        <v>509</v>
       </c>
       <c r="G101">
         <v>-11.64868566292302</v>
@@ -4391,16 +4883,16 @@
         <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E102" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="F102" t="s">
-        <v>447</v>
+        <v>510</v>
       </c>
       <c r="G102">
         <v>-12.19737106455074</v>
@@ -4417,16 +4909,16 @@
         <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E103" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="F103" t="s">
-        <v>448</v>
+        <v>511</v>
       </c>
       <c r="G103">
         <v>-12.19222521573667</v>
@@ -4443,16 +4935,16 @@
         <v>10</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D104" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E104" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="F104" t="s">
-        <v>449</v>
+        <v>512</v>
       </c>
       <c r="G104">
         <v>-12.20977758513438</v>
@@ -4469,16 +4961,16 @@
         <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D105" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E105" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="F105" t="s">
-        <v>450</v>
+        <v>513</v>
       </c>
       <c r="G105">
         <v>-12.19484291331598</v>
@@ -4495,16 +4987,16 @@
         <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D106" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E106" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="F106" t="s">
-        <v>451</v>
+        <v>514</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4515,16 +5007,16 @@
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D107" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E107" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="F107" t="s">
-        <v>451</v>
+        <v>514</v>
       </c>
       <c r="G107">
         <v>-12.20224155888374</v>
@@ -4541,16 +5033,16 @@
         <v>10</v>
       </c>
       <c r="C108" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D108" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E108" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="F108" t="s">
-        <v>452</v>
+        <v>515</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -4561,16 +5053,16 @@
         <v>10</v>
       </c>
       <c r="C109" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D109" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E109" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="F109" t="s">
-        <v>453</v>
+        <v>516</v>
       </c>
       <c r="G109">
         <v>-12.23414262482221</v>
@@ -4587,16 +5079,16 @@
         <v>10</v>
       </c>
       <c r="C110" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D110" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E110" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="F110" t="s">
-        <v>454</v>
+        <v>517</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -4607,16 +5099,16 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D111" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E111" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="F111" t="s">
-        <v>455</v>
+        <v>518</v>
       </c>
       <c r="G111">
         <v>-12.23925412603609</v>
@@ -4633,16 +5125,16 @@
         <v>10</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E112" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="F112" t="s">
-        <v>456</v>
+        <v>519</v>
       </c>
       <c r="G112">
         <v>-12.23564566734995</v>
@@ -4659,16 +5151,16 @@
         <v>10</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D113" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E113" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="F113" t="s">
-        <v>457</v>
+        <v>520</v>
       </c>
       <c r="G113">
         <v>-12.24288395644702</v>
@@ -4685,16 +5177,16 @@
         <v>10</v>
       </c>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D114" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E114" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="F114" t="s">
-        <v>458</v>
+        <v>521</v>
       </c>
       <c r="G114">
         <v>-12.23571408750851</v>
@@ -4711,16 +5203,16 @@
         <v>10</v>
       </c>
       <c r="C115" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D115" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E115" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="F115" t="s">
-        <v>459</v>
+        <v>522</v>
       </c>
       <c r="G115">
         <v>-12.24833258243775</v>
@@ -4737,16 +5229,16 @@
         <v>10</v>
       </c>
       <c r="C116" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D116" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E116" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="F116" t="s">
-        <v>460</v>
+        <v>523</v>
       </c>
       <c r="G116">
         <v>-12.25431732384045</v>
@@ -4763,16 +5255,16 @@
         <v>10</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D117" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E117" t="s">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="F117" t="s">
-        <v>461</v>
+        <v>524</v>
       </c>
       <c r="G117">
         <v>-12.2489985288183</v>
@@ -4789,16 +5281,16 @@
         <v>10</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D118" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E118" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="F118" t="s">
-        <v>462</v>
+        <v>525</v>
       </c>
       <c r="G118">
         <v>-12.26963641612595</v>
@@ -4815,16 +5307,16 @@
         <v>10</v>
       </c>
       <c r="C119" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D119" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E119" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="F119" t="s">
-        <v>463</v>
+        <v>526</v>
       </c>
       <c r="G119">
         <v>-12.24515911108584</v>
@@ -4841,16 +5333,16 @@
         <v>10</v>
       </c>
       <c r="C120" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D120" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E120" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="F120" t="s">
-        <v>411</v>
+        <v>474</v>
       </c>
       <c r="G120">
         <v>-12.27236795835944</v>
@@ -4867,16 +5359,16 @@
         <v>10</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D121" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E121" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="F121" t="s">
-        <v>411</v>
+        <v>474</v>
       </c>
       <c r="G121">
         <v>-12.23801036263309</v>
@@ -4893,16 +5385,16 @@
         <v>10</v>
       </c>
       <c r="C122" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E122" t="s">
-        <v>154</v>
+        <v>203</v>
       </c>
       <c r="F122" t="s">
-        <v>464</v>
+        <v>527</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4912,14 +5404,17 @@
       <c r="B123" t="s">
         <v>10</v>
       </c>
+      <c r="C123" t="s">
+        <v>20</v>
+      </c>
       <c r="D123" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E123" t="s">
-        <v>155</v>
+        <v>204</v>
       </c>
       <c r="F123" t="s">
-        <v>465</v>
+        <v>528</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4929,14 +5424,17 @@
       <c r="B124" t="s">
         <v>10</v>
       </c>
+      <c r="C124" t="s">
+        <v>20</v>
+      </c>
       <c r="D124" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E124" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="F124" t="s">
-        <v>466</v>
+        <v>529</v>
       </c>
       <c r="G124">
         <v>-12.28652309319805</v>
@@ -4952,14 +5450,17 @@
       <c r="B125" t="s">
         <v>10</v>
       </c>
+      <c r="C125" t="s">
+        <v>20</v>
+      </c>
       <c r="D125" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E125" t="s">
-        <v>157</v>
+        <v>206</v>
       </c>
       <c r="F125" t="s">
-        <v>467</v>
+        <v>530</v>
       </c>
       <c r="G125">
         <v>-12.28326406155833</v>
@@ -4975,14 +5476,17 @@
       <c r="B126" t="s">
         <v>10</v>
       </c>
+      <c r="C126" t="s">
+        <v>20</v>
+      </c>
       <c r="D126" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E126" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="F126" t="s">
-        <v>468</v>
+        <v>531</v>
       </c>
       <c r="G126">
         <v>-12.28239214971529</v>
@@ -4998,14 +5502,17 @@
       <c r="B127" t="s">
         <v>10</v>
       </c>
+      <c r="C127" t="s">
+        <v>20</v>
+      </c>
       <c r="D127" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E127" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="F127" t="s">
-        <v>469</v>
+        <v>532</v>
       </c>
       <c r="G127">
         <v>-12.26574600460814</v>
@@ -5021,14 +5528,17 @@
       <c r="B128" t="s">
         <v>10</v>
       </c>
+      <c r="C128" t="s">
+        <v>20</v>
+      </c>
       <c r="D128" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E128" t="s">
-        <v>160</v>
+        <v>209</v>
       </c>
       <c r="F128" t="s">
-        <v>390</v>
+        <v>453</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -5038,14 +5548,17 @@
       <c r="B129" t="s">
         <v>10</v>
       </c>
+      <c r="C129" t="s">
+        <v>20</v>
+      </c>
       <c r="D129" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E129" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="F129" t="s">
-        <v>390</v>
+        <v>453</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -5056,16 +5569,16 @@
         <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D130" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E130" t="s">
-        <v>162</v>
+        <v>211</v>
       </c>
       <c r="F130" t="s">
-        <v>470</v>
+        <v>533</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -5076,10 +5589,16 @@
         <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="D131" t="s">
+        <v>56</v>
+      </c>
+      <c r="E131" t="s">
+        <v>212</v>
       </c>
       <c r="F131" t="s">
-        <v>471</v>
+        <v>534</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -5090,10 +5609,16 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="D132" t="s">
+        <v>56</v>
+      </c>
+      <c r="E132" t="s">
+        <v>213</v>
       </c>
       <c r="F132" t="s">
-        <v>472</v>
+        <v>535</v>
       </c>
       <c r="G132">
         <v>-11.7199316</v>
@@ -5110,10 +5635,16 @@
         <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="D133" t="s">
+        <v>56</v>
+      </c>
+      <c r="E133" t="s">
+        <v>214</v>
       </c>
       <c r="F133" t="s">
-        <v>473</v>
+        <v>536</v>
       </c>
       <c r="G133">
         <v>-11.7184486</v>
@@ -5130,16 +5661,16 @@
         <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D134" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E134" t="s">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="F134" t="s">
-        <v>474</v>
+        <v>537</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -5150,16 +5681,16 @@
         <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D135" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E135" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="F135" t="s">
-        <v>475</v>
+        <v>538</v>
       </c>
       <c r="G135">
         <v>-11.7386809</v>
@@ -5176,16 +5707,16 @@
         <v>11</v>
       </c>
       <c r="C136" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D136" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E136" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="F136" t="s">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="G136">
         <v>-11.7855211</v>
@@ -5202,16 +5733,16 @@
         <v>11</v>
       </c>
       <c r="C137" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D137" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E137" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="F137" t="s">
-        <v>477</v>
+        <v>540</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -5222,16 +5753,16 @@
         <v>11</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D138" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E138" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="F138" t="s">
-        <v>478</v>
+        <v>541</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -5242,16 +5773,16 @@
         <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D139" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E139" t="s">
-        <v>168</v>
+        <v>220</v>
       </c>
       <c r="F139" t="s">
-        <v>479</v>
+        <v>542</v>
       </c>
       <c r="G139">
         <v>-11.7757808</v>
@@ -5268,16 +5799,16 @@
         <v>11</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D140" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E140" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="F140" t="s">
-        <v>480</v>
+        <v>543</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -5288,16 +5819,16 @@
         <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D141" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E141" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="F141" t="s">
-        <v>481</v>
+        <v>544</v>
       </c>
       <c r="G141">
         <v>-11.7741939</v>
@@ -5314,16 +5845,16 @@
         <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D142" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E142" t="s">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="F142" t="s">
-        <v>481</v>
+        <v>544</v>
       </c>
       <c r="G142">
         <v>-11.58540886618898</v>
@@ -5340,16 +5871,16 @@
         <v>11</v>
       </c>
       <c r="C143" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D143" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E143" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="F143" t="s">
-        <v>482</v>
+        <v>545</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -5360,16 +5891,16 @@
         <v>11</v>
       </c>
       <c r="C144" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D144" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E144" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="F144" t="s">
-        <v>483</v>
+        <v>546</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -5380,16 +5911,16 @@
         <v>11</v>
       </c>
       <c r="C145" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D145" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E145" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="F145" t="s">
-        <v>484</v>
+        <v>547</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -5400,16 +5931,16 @@
         <v>11</v>
       </c>
       <c r="C146" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D146" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E146" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="F146" t="s">
-        <v>485</v>
+        <v>548</v>
       </c>
       <c r="G146">
         <v>-11.7747038</v>
@@ -5426,16 +5957,16 @@
         <v>11</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D147" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E147" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="F147" t="s">
-        <v>486</v>
+        <v>549</v>
       </c>
       <c r="G147">
         <v>-11.7671406</v>
@@ -5452,16 +5983,16 @@
         <v>11</v>
       </c>
       <c r="C148" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D148" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E148" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="F148" t="s">
-        <v>487</v>
+        <v>550</v>
       </c>
       <c r="G148">
         <v>-11.7589678</v>
@@ -5478,16 +6009,16 @@
         <v>11</v>
       </c>
       <c r="C149" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D149" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E149" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="F149" t="s">
-        <v>488</v>
+        <v>551</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5498,16 +6029,16 @@
         <v>11</v>
       </c>
       <c r="C150" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D150" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E150" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="F150" t="s">
-        <v>489</v>
+        <v>552</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5518,16 +6049,16 @@
         <v>11</v>
       </c>
       <c r="C151" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D151" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E151" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="F151" t="s">
-        <v>490</v>
+        <v>553</v>
       </c>
       <c r="G151">
         <v>-11.82436430093914</v>
@@ -5544,16 +6075,16 @@
         <v>11</v>
       </c>
       <c r="C152" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D152" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E152" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="F152" t="s">
-        <v>491</v>
+        <v>554</v>
       </c>
       <c r="G152">
         <v>-11.80992950054916</v>
@@ -5570,16 +6101,16 @@
         <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D153" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E153" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="F153" t="s">
-        <v>492</v>
+        <v>555</v>
       </c>
       <c r="G153">
         <v>-11.84136164374853</v>
@@ -5596,16 +6127,16 @@
         <v>11</v>
       </c>
       <c r="C154" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D154" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E154" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="F154" t="s">
-        <v>493</v>
+        <v>556</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5616,16 +6147,16 @@
         <v>11</v>
       </c>
       <c r="C155" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D155" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E155" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="F155" t="s">
-        <v>494</v>
+        <v>557</v>
       </c>
       <c r="G155">
         <v>-11.81016976394841</v>
@@ -5642,16 +6173,16 @@
         <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D156" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E156" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="F156" t="s">
-        <v>495</v>
+        <v>558</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5662,16 +6193,16 @@
         <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D157" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E157" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="F157" t="s">
-        <v>496</v>
+        <v>559</v>
       </c>
       <c r="G157">
         <v>-11.8362673</v>
@@ -5688,16 +6219,16 @@
         <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D158" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E158" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="F158" t="s">
-        <v>497</v>
+        <v>560</v>
       </c>
       <c r="G158">
         <v>-11.84836602898079</v>
@@ -5714,16 +6245,16 @@
         <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D159" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E159" t="s">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="F159" t="s">
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="G159">
         <v>-11.8528743007735</v>
@@ -5740,16 +6271,16 @@
         <v>11</v>
       </c>
       <c r="C160" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D160" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E160" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="F160" t="s">
-        <v>499</v>
+        <v>562</v>
       </c>
       <c r="G160">
         <v>-11.8528894</v>
@@ -5766,16 +6297,16 @@
         <v>11</v>
       </c>
       <c r="C161" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D161" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E161" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="F161" t="s">
-        <v>500</v>
+        <v>563</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5786,16 +6317,16 @@
         <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D162" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E162" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="F162" t="s">
-        <v>501</v>
+        <v>564</v>
       </c>
       <c r="G162">
         <v>-11.88207276688416</v>
@@ -5812,16 +6343,16 @@
         <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D163" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E163" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="F163" t="s">
-        <v>502</v>
+        <v>565</v>
       </c>
       <c r="G163">
         <v>-11.8668334</v>
@@ -5838,16 +6369,16 @@
         <v>11</v>
       </c>
       <c r="C164" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D164" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E164" t="s">
-        <v>193</v>
+        <v>245</v>
       </c>
       <c r="F164" t="s">
-        <v>503</v>
+        <v>566</v>
       </c>
       <c r="G164">
         <v>-11.88927876471597</v>
@@ -5864,16 +6395,16 @@
         <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D165" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E165" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="F165" t="s">
-        <v>504</v>
+        <v>567</v>
       </c>
       <c r="G165">
         <v>-11.8746048</v>
@@ -5890,16 +6421,16 @@
         <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D166" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E166" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="F166" t="s">
-        <v>505</v>
+        <v>568</v>
       </c>
       <c r="G166">
         <v>-11.88443241298675</v>
@@ -5916,16 +6447,16 @@
         <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D167" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E167" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="F167" t="s">
-        <v>506</v>
+        <v>569</v>
       </c>
       <c r="G167">
         <v>-11.88702290869847</v>
@@ -5942,16 +6473,16 @@
         <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D168" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E168" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="F168" t="s">
-        <v>507</v>
+        <v>570</v>
       </c>
       <c r="G168">
         <v>-11.85904292197132</v>
@@ -5968,16 +6499,16 @@
         <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D169" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E169" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
       <c r="F169" t="s">
-        <v>508</v>
+        <v>571</v>
       </c>
       <c r="G169">
         <v>-11.85904292197132</v>
@@ -5994,16 +6525,16 @@
         <v>11</v>
       </c>
       <c r="C170" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D170" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E170" t="s">
-        <v>199</v>
+        <v>251</v>
       </c>
       <c r="F170" t="s">
-        <v>509</v>
+        <v>572</v>
       </c>
       <c r="G170">
         <v>-11.85439443206664</v>
@@ -6020,16 +6551,16 @@
         <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D171" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E171" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="F171" t="s">
-        <v>510</v>
+        <v>573</v>
       </c>
       <c r="G171">
         <v>-11.85964832372679</v>
@@ -6046,16 +6577,16 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D172" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E172" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="F172" t="s">
-        <v>511</v>
+        <v>574</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -6066,16 +6597,16 @@
         <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D173" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E173" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="F173" t="s">
-        <v>512</v>
+        <v>575</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -6086,16 +6617,16 @@
         <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D174" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E174" t="s">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="F174" t="s">
-        <v>513</v>
+        <v>576</v>
       </c>
       <c r="G174">
         <v>-11.902989</v>
@@ -6112,16 +6643,16 @@
         <v>11</v>
       </c>
       <c r="C175" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D175" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E175" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="F175" t="s">
-        <v>514</v>
+        <v>577</v>
       </c>
       <c r="G175">
         <v>-11.88940362427</v>
@@ -6138,16 +6669,16 @@
         <v>11</v>
       </c>
       <c r="C176" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D176" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E176" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="F176" t="s">
-        <v>515</v>
+        <v>578</v>
       </c>
       <c r="G176">
         <v>-11.85119757695296</v>
@@ -6164,16 +6695,16 @@
         <v>11</v>
       </c>
       <c r="C177" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D177" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E177" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="F177" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6184,16 +6715,16 @@
         <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D178" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E178" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="F178" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -6204,16 +6735,16 @@
         <v>11</v>
       </c>
       <c r="C179" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D179" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E179" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="F179" t="s">
-        <v>516</v>
+        <v>579</v>
       </c>
       <c r="G179">
         <v>-11.8808683</v>
@@ -6230,16 +6761,16 @@
         <v>11</v>
       </c>
       <c r="C180" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D180" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E180" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="F180" t="s">
-        <v>517</v>
+        <v>580</v>
       </c>
       <c r="G180">
         <v>-11.86293770637044</v>
@@ -6256,16 +6787,16 @@
         <v>11</v>
       </c>
       <c r="C181" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D181" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E181" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="F181" t="s">
-        <v>518</v>
+        <v>581</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -6276,16 +6807,16 @@
         <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D182" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E182" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="F182" t="s">
-        <v>519</v>
+        <v>582</v>
       </c>
       <c r="G182">
         <v>-11.8601053</v>
@@ -6302,16 +6833,16 @@
         <v>11</v>
       </c>
       <c r="C183" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D183" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E183" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="F183" t="s">
-        <v>520</v>
+        <v>583</v>
       </c>
       <c r="G183">
         <v>-11.8865711</v>
@@ -6328,16 +6859,16 @@
         <v>11</v>
       </c>
       <c r="C184" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D184" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E184" t="s">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="F184" t="s">
-        <v>521</v>
+        <v>584</v>
       </c>
       <c r="G184">
         <v>-11.91274450244943</v>
@@ -6354,16 +6885,16 @@
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D185" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E185" t="s">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="F185" t="s">
-        <v>522</v>
+        <v>585</v>
       </c>
       <c r="G185">
         <v>-11.91492181212855</v>
@@ -6380,16 +6911,16 @@
         <v>11</v>
       </c>
       <c r="C186" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D186" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E186" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="F186" t="s">
-        <v>523</v>
+        <v>586</v>
       </c>
       <c r="G186">
         <v>-11.89838779171314</v>
@@ -6406,16 +6937,16 @@
         <v>11</v>
       </c>
       <c r="C187" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D187" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E187" t="s">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="F187" t="s">
-        <v>524</v>
+        <v>587</v>
       </c>
       <c r="G187">
         <v>-11.9247875</v>
@@ -6432,16 +6963,16 @@
         <v>11</v>
       </c>
       <c r="C188" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D188" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E188" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="F188" t="s">
-        <v>525</v>
+        <v>588</v>
       </c>
       <c r="G188">
         <v>-11.9190778</v>
@@ -6458,16 +6989,16 @@
         <v>11</v>
       </c>
       <c r="C189" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D189" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E189" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="F189" t="s">
-        <v>526</v>
+        <v>589</v>
       </c>
       <c r="G189">
         <v>-11.911239</v>
@@ -6484,16 +7015,16 @@
         <v>11</v>
       </c>
       <c r="C190" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D190" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E190" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="F190" t="s">
-        <v>527</v>
+        <v>590</v>
       </c>
       <c r="G190">
         <v>-11.8278645</v>
@@ -6510,16 +7041,16 @@
         <v>11</v>
       </c>
       <c r="C191" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D191" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E191" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="F191" t="s">
-        <v>528</v>
+        <v>591</v>
       </c>
       <c r="G191">
         <v>-11.8414672716532</v>
@@ -6536,16 +7067,16 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D192" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E192" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="F192" t="s">
-        <v>529</v>
+        <v>592</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -6556,16 +7087,16 @@
         <v>11</v>
       </c>
       <c r="C193" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D193" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E193" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="F193" t="s">
-        <v>530</v>
+        <v>593</v>
       </c>
       <c r="G193">
         <v>-11.77602036332376</v>
@@ -6582,16 +7113,16 @@
         <v>11</v>
       </c>
       <c r="C194" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D194" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E194" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="F194" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="G194">
         <v>-11.7959112</v>
@@ -6608,16 +7139,16 @@
         <v>11</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D195" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E195" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="F195" t="s">
-        <v>532</v>
+        <v>595</v>
       </c>
       <c r="G195">
         <v>-11.7580867</v>
@@ -6634,16 +7165,16 @@
         <v>11</v>
       </c>
       <c r="C196" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D196" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E196" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="F196" t="s">
-        <v>533</v>
+        <v>596</v>
       </c>
       <c r="G196">
         <v>-11.7632851</v>
@@ -6660,16 +7191,16 @@
         <v>11</v>
       </c>
       <c r="C197" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D197" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E197" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="F197" t="s">
-        <v>533</v>
+        <v>596</v>
       </c>
       <c r="G197">
         <v>-11.40882116931708</v>
@@ -6686,16 +7217,16 @@
         <v>11</v>
       </c>
       <c r="C198" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E198" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="F198" t="s">
-        <v>534</v>
+        <v>597</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6706,16 +7237,16 @@
         <v>11</v>
       </c>
       <c r="C199" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D199" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E199" t="s">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="F199" t="s">
-        <v>535</v>
+        <v>598</v>
       </c>
       <c r="G199">
         <v>-11.89097182883893</v>
@@ -6732,16 +7263,16 @@
         <v>11</v>
       </c>
       <c r="C200" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D200" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E200" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="F200" t="s">
-        <v>536</v>
+        <v>599</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -6752,16 +7283,16 @@
         <v>11</v>
       </c>
       <c r="C201" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D201" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E201" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="F201" t="s">
-        <v>537</v>
+        <v>600</v>
       </c>
       <c r="G201">
         <v>-11.89605097374183</v>
@@ -6778,16 +7309,16 @@
         <v>11</v>
       </c>
       <c r="C202" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D202" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E202" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="F202" t="s">
-        <v>538</v>
+        <v>601</v>
       </c>
       <c r="G202">
         <v>-11.87151072120418</v>
@@ -6804,16 +7335,16 @@
         <v>11</v>
       </c>
       <c r="C203" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D203" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E203" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="F203" t="s">
-        <v>539</v>
+        <v>602</v>
       </c>
       <c r="G203">
         <v>-11.86990225883718</v>
@@ -6830,16 +7361,16 @@
         <v>11</v>
       </c>
       <c r="C204" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D204" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E204" t="s">
-        <v>233</v>
+        <v>285</v>
       </c>
       <c r="F204" t="s">
-        <v>540</v>
+        <v>603</v>
       </c>
       <c r="G204">
         <v>-11.85504067822945</v>
@@ -6856,16 +7387,16 @@
         <v>11</v>
       </c>
       <c r="C205" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D205" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E205" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="F205" t="s">
-        <v>541</v>
+        <v>604</v>
       </c>
       <c r="G205">
         <v>-11.89023668146737</v>
@@ -6882,16 +7413,16 @@
         <v>11</v>
       </c>
       <c r="C206" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D206" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E206" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="F206" t="s">
-        <v>542</v>
+        <v>605</v>
       </c>
       <c r="G206">
         <v>-11.88428639896506</v>
@@ -6908,16 +7439,16 @@
         <v>11</v>
       </c>
       <c r="C207" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D207" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E207" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="F207" t="s">
-        <v>543</v>
+        <v>606</v>
       </c>
       <c r="G207">
         <v>-11.88078433190155</v>
@@ -6934,16 +7465,16 @@
         <v>11</v>
       </c>
       <c r="C208" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E208" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="F208" t="s">
-        <v>544</v>
+        <v>607</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6954,16 +7485,16 @@
         <v>11</v>
       </c>
       <c r="C209" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E209" t="s">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="F209" t="s">
-        <v>545</v>
+        <v>608</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6974,16 +7505,16 @@
         <v>11</v>
       </c>
       <c r="C210" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E210" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="F210" t="s">
-        <v>546</v>
+        <v>609</v>
       </c>
       <c r="G210">
         <v>-11.63611416204234</v>
@@ -7000,16 +7531,16 @@
         <v>11</v>
       </c>
       <c r="C211" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E211" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="F211" t="s">
-        <v>547</v>
+        <v>610</v>
       </c>
       <c r="G211">
         <v>-11.64921932362798</v>
@@ -7026,16 +7557,16 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E212" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="F212" t="s">
-        <v>548</v>
+        <v>611</v>
       </c>
       <c r="G212">
         <v>-11.63357632324934</v>
@@ -7052,16 +7583,16 @@
         <v>11</v>
       </c>
       <c r="C213" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E213" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
       <c r="F213" t="s">
-        <v>549</v>
+        <v>612</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -7072,16 +7603,16 @@
         <v>11</v>
       </c>
       <c r="C214" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E214" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="F214" t="s">
-        <v>550</v>
+        <v>613</v>
       </c>
       <c r="G214">
         <v>-11.6459983857482</v>
@@ -7098,16 +7629,16 @@
         <v>11</v>
       </c>
       <c r="C215" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D215" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E215" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="F215" t="s">
-        <v>551</v>
+        <v>614</v>
       </c>
       <c r="G215">
         <v>-11.66847338006906</v>
@@ -7124,16 +7655,16 @@
         <v>11</v>
       </c>
       <c r="C216" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D216" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E216" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="F216" t="s">
-        <v>552</v>
+        <v>615</v>
       </c>
       <c r="G216">
         <v>-11.66072461199041</v>
@@ -7150,16 +7681,16 @@
         <v>11</v>
       </c>
       <c r="C217" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D217" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E217" t="s">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="F217" t="s">
-        <v>553</v>
+        <v>616</v>
       </c>
       <c r="G217">
         <v>-11.61380764667526</v>
@@ -7176,10 +7707,16 @@
         <v>11</v>
       </c>
       <c r="C218" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>67</v>
+      </c>
+      <c r="E218" t="s">
+        <v>299</v>
       </c>
       <c r="F218" t="s">
-        <v>554</v>
+        <v>617</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -7190,10 +7727,16 @@
         <v>11</v>
       </c>
       <c r="C219" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D219" t="s">
+        <v>67</v>
+      </c>
+      <c r="E219" t="s">
+        <v>300</v>
       </c>
       <c r="F219" t="s">
-        <v>481</v>
+        <v>544</v>
       </c>
       <c r="G219">
         <v>-11.7741939</v>
@@ -7210,10 +7753,16 @@
         <v>11</v>
       </c>
       <c r="C220" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D220" t="s">
+        <v>67</v>
+      </c>
+      <c r="E220" t="s">
+        <v>301</v>
       </c>
       <c r="F220" t="s">
-        <v>481</v>
+        <v>544</v>
       </c>
       <c r="G220">
         <v>-11.58540886618898</v>
@@ -7230,10 +7779,16 @@
         <v>11</v>
       </c>
       <c r="C221" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D221" t="s">
+        <v>67</v>
+      </c>
+      <c r="E221" t="s">
+        <v>302</v>
       </c>
       <c r="F221" t="s">
-        <v>555</v>
+        <v>618</v>
       </c>
       <c r="G221">
         <v>-11.57131205875416</v>
@@ -7250,10 +7805,16 @@
         <v>11</v>
       </c>
       <c r="C222" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D222" t="s">
+        <v>67</v>
+      </c>
+      <c r="E222" t="s">
+        <v>303</v>
       </c>
       <c r="F222" t="s">
-        <v>556</v>
+        <v>619</v>
       </c>
       <c r="G222">
         <v>-11.61046307805619</v>
@@ -7270,10 +7831,16 @@
         <v>11</v>
       </c>
       <c r="C223" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D223" t="s">
+        <v>67</v>
+      </c>
+      <c r="E223" t="s">
+        <v>304</v>
       </c>
       <c r="F223" t="s">
-        <v>557</v>
+        <v>620</v>
       </c>
       <c r="G223">
         <v>-11.60352566305956</v>
@@ -7290,10 +7857,16 @@
         <v>11</v>
       </c>
       <c r="C224" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="D224" t="s">
+        <v>67</v>
+      </c>
+      <c r="E224" t="s">
+        <v>305</v>
       </c>
       <c r="F224" t="s">
-        <v>558</v>
+        <v>621</v>
       </c>
       <c r="G224">
         <v>-11.62207595151043</v>
@@ -7310,16 +7883,16 @@
         <v>11</v>
       </c>
       <c r="C225" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D225" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E225" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="F225" t="s">
-        <v>559</v>
+        <v>622</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -7330,16 +7903,16 @@
         <v>11</v>
       </c>
       <c r="C226" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D226" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E226" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="F226" t="s">
-        <v>560</v>
+        <v>623</v>
       </c>
       <c r="G226">
         <v>-11.70926187312358</v>
@@ -7356,16 +7929,16 @@
         <v>11</v>
       </c>
       <c r="C227" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D227" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E227" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="F227" t="s">
-        <v>561</v>
+        <v>624</v>
       </c>
       <c r="G227">
         <v>-11.69737505682969</v>
@@ -7382,16 +7955,16 @@
         <v>11</v>
       </c>
       <c r="C228" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D228" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E228" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="F228" t="s">
-        <v>562</v>
+        <v>625</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -7402,16 +7975,16 @@
         <v>11</v>
       </c>
       <c r="C229" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D229" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E229" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F229" t="s">
-        <v>563</v>
+        <v>626</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -7422,16 +7995,16 @@
         <v>11</v>
       </c>
       <c r="C230" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D230" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E230" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="F230" t="s">
-        <v>564</v>
+        <v>627</v>
       </c>
       <c r="G230">
         <v>-11.72714747108566</v>
@@ -7448,16 +8021,16 @@
         <v>11</v>
       </c>
       <c r="C231" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D231" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E231" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="F231" t="s">
-        <v>565</v>
+        <v>628</v>
       </c>
       <c r="G231">
         <v>-11.71386165097744</v>
@@ -7474,16 +8047,16 @@
         <v>11</v>
       </c>
       <c r="C232" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D232" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E232" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F232" t="s">
-        <v>566</v>
+        <v>629</v>
       </c>
       <c r="G232">
         <v>-11.70111317997415</v>
@@ -7500,16 +8073,16 @@
         <v>11</v>
       </c>
       <c r="C233" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E233" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="F233" t="s">
-        <v>567</v>
+        <v>630</v>
       </c>
       <c r="G233">
         <v>-11.6934069464393</v>
@@ -7526,16 +8099,16 @@
         <v>11</v>
       </c>
       <c r="C234" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D234" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E234" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="F234" t="s">
-        <v>568</v>
+        <v>631</v>
       </c>
       <c r="G234">
         <v>-11.69062441838844</v>
@@ -7552,16 +8125,16 @@
         <v>11</v>
       </c>
       <c r="C235" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D235" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E235" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="F235" t="s">
-        <v>569</v>
+        <v>632</v>
       </c>
       <c r="G235">
         <v>-11.67388143558751</v>
@@ -7578,16 +8151,16 @@
         <v>11</v>
       </c>
       <c r="C236" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D236" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E236" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="F236" t="s">
-        <v>570</v>
+        <v>633</v>
       </c>
       <c r="G236">
         <v>-11.69115791141486</v>
@@ -7604,16 +8177,16 @@
         <v>11</v>
       </c>
       <c r="C237" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D237" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E237" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="F237" t="s">
-        <v>571</v>
+        <v>634</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -7624,16 +8197,16 @@
         <v>11</v>
       </c>
       <c r="C238" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D238" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E238" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="F238" t="s">
-        <v>572</v>
+        <v>635</v>
       </c>
       <c r="G238">
         <v>-11.50333713023055</v>
@@ -7650,16 +8223,16 @@
         <v>11</v>
       </c>
       <c r="C239" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D239" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E239" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="F239" t="s">
-        <v>573</v>
+        <v>636</v>
       </c>
       <c r="G239">
         <v>-11.51218112137282</v>
@@ -7676,16 +8249,16 @@
         <v>11</v>
       </c>
       <c r="C240" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D240" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E240" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="F240" t="s">
-        <v>574</v>
+        <v>637</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -7696,16 +8269,16 @@
         <v>11</v>
       </c>
       <c r="C241" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D241" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E241" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="F241" t="s">
-        <v>575</v>
+        <v>638</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -7716,16 +8289,16 @@
         <v>11</v>
       </c>
       <c r="C242" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D242" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E242" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F242" t="s">
-        <v>576</v>
+        <v>639</v>
       </c>
       <c r="G242">
         <v>-11.48978536633614</v>
@@ -7742,16 +8315,16 @@
         <v>11</v>
       </c>
       <c r="C243" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D243" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E243" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="F243" t="s">
-        <v>577</v>
+        <v>640</v>
       </c>
       <c r="G243">
         <v>-11.54578565320765</v>
@@ -7768,16 +8341,16 @@
         <v>11</v>
       </c>
       <c r="C244" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D244" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E244" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
       <c r="F244" t="s">
-        <v>578</v>
+        <v>641</v>
       </c>
       <c r="G244">
         <v>-11.50154408896333</v>
@@ -7794,16 +8367,16 @@
         <v>11</v>
       </c>
       <c r="C245" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D245" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E245" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="F245" t="s">
-        <v>579</v>
+        <v>642</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -7814,16 +8387,16 @@
         <v>11</v>
       </c>
       <c r="C246" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D246" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E246" t="s">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="F246" t="s">
-        <v>580</v>
+        <v>643</v>
       </c>
       <c r="G246">
         <v>-11.51793362814303</v>
@@ -7840,16 +8413,16 @@
         <v>11</v>
       </c>
       <c r="C247" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D247" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E247" t="s">
-        <v>269</v>
+        <v>328</v>
       </c>
       <c r="F247" t="s">
-        <v>581</v>
+        <v>644</v>
       </c>
       <c r="G247">
         <v>-11.52157343091736</v>
@@ -7866,16 +8439,16 @@
         <v>11</v>
       </c>
       <c r="C248" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D248" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E248" t="s">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="F248" t="s">
-        <v>582</v>
+        <v>645</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -7886,16 +8459,16 @@
         <v>11</v>
       </c>
       <c r="C249" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D249" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E249" t="s">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="F249" t="s">
-        <v>583</v>
+        <v>646</v>
       </c>
       <c r="G249">
         <v>-11.47096842654614</v>
@@ -7912,16 +8485,16 @@
         <v>11</v>
       </c>
       <c r="C250" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D250" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E250" t="s">
-        <v>272</v>
+        <v>331</v>
       </c>
       <c r="F250" t="s">
-        <v>584</v>
+        <v>647</v>
       </c>
       <c r="G250">
         <v>-11.48747353957027</v>
@@ -7938,16 +8511,16 @@
         <v>11</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D251" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E251" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="F251" t="s">
-        <v>585</v>
+        <v>648</v>
       </c>
       <c r="G251">
         <v>-11.46614794319647</v>
@@ -7964,16 +8537,16 @@
         <v>11</v>
       </c>
       <c r="C252" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D252" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E252" t="s">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="F252" t="s">
-        <v>586</v>
+        <v>649</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -7984,16 +8557,16 @@
         <v>11</v>
       </c>
       <c r="C253" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D253" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E253" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="F253" t="s">
-        <v>587</v>
+        <v>650</v>
       </c>
       <c r="G253">
         <v>-11.46858507749499</v>
@@ -8010,16 +8583,16 @@
         <v>11</v>
       </c>
       <c r="C254" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D254" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E254" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="F254" t="s">
-        <v>588</v>
+        <v>651</v>
       </c>
       <c r="G254">
         <v>-11.47572933779153</v>
@@ -8036,16 +8609,16 @@
         <v>11</v>
       </c>
       <c r="C255" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D255" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E255" t="s">
-        <v>277</v>
+        <v>336</v>
       </c>
       <c r="F255" t="s">
-        <v>589</v>
+        <v>652</v>
       </c>
       <c r="G255">
         <v>-11.47665238153512</v>
@@ -8062,16 +8635,16 @@
         <v>11</v>
       </c>
       <c r="C256" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D256" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E256" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="F256" t="s">
-        <v>590</v>
+        <v>653</v>
       </c>
       <c r="G256">
         <v>-11.45968069783523</v>
@@ -8088,16 +8661,16 @@
         <v>11</v>
       </c>
       <c r="C257" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D257" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E257" t="s">
-        <v>279</v>
+        <v>338</v>
       </c>
       <c r="F257" t="s">
-        <v>591</v>
+        <v>654</v>
       </c>
       <c r="G257">
         <v>-11.45757424275266</v>
@@ -8114,16 +8687,16 @@
         <v>11</v>
       </c>
       <c r="C258" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D258" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E258" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="F258" t="s">
-        <v>592</v>
+        <v>655</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -8134,16 +8707,16 @@
         <v>11</v>
       </c>
       <c r="C259" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D259" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E259" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="F259" t="s">
-        <v>593</v>
+        <v>656</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -8154,16 +8727,16 @@
         <v>11</v>
       </c>
       <c r="C260" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D260" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E260" t="s">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="F260" t="s">
-        <v>594</v>
+        <v>657</v>
       </c>
       <c r="G260">
         <v>-11.41391903952383</v>
@@ -8180,16 +8753,16 @@
         <v>11</v>
       </c>
       <c r="C261" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D261" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E261" t="s">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c r="F261" t="s">
-        <v>595</v>
+        <v>658</v>
       </c>
       <c r="G261">
         <v>-11.43192125204272</v>
@@ -8206,16 +8779,16 @@
         <v>11</v>
       </c>
       <c r="C262" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D262" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E262" t="s">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="F262" t="s">
-        <v>596</v>
+        <v>659</v>
       </c>
       <c r="G262">
         <v>-11.4213265914408</v>
@@ -8232,16 +8805,16 @@
         <v>11</v>
       </c>
       <c r="C263" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D263" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E263" t="s">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="F263" t="s">
-        <v>597</v>
+        <v>660</v>
       </c>
       <c r="G263">
         <v>-11.44229465950162</v>
@@ -8258,16 +8831,16 @@
         <v>11</v>
       </c>
       <c r="C264" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D264" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E264" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="F264" t="s">
-        <v>598</v>
+        <v>661</v>
       </c>
       <c r="G264">
         <v>-11.43183300103182</v>
@@ -8284,16 +8857,16 @@
         <v>11</v>
       </c>
       <c r="C265" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D265" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E265" t="s">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="F265" t="s">
-        <v>599</v>
+        <v>662</v>
       </c>
       <c r="G265">
         <v>-11.48267112010393</v>
@@ -8309,8 +8882,17 @@
       <c r="B266" t="s">
         <v>11</v>
       </c>
+      <c r="C266" t="s">
+        <v>27</v>
+      </c>
+      <c r="D266" t="s">
+        <v>72</v>
+      </c>
+      <c r="E266" t="s">
+        <v>347</v>
+      </c>
       <c r="F266" t="s">
-        <v>600</v>
+        <v>663</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -8320,8 +8902,17 @@
       <c r="B267" t="s">
         <v>11</v>
       </c>
+      <c r="C267" t="s">
+        <v>27</v>
+      </c>
+      <c r="D267" t="s">
+        <v>72</v>
+      </c>
+      <c r="E267" t="s">
+        <v>348</v>
+      </c>
       <c r="F267" t="s">
-        <v>601</v>
+        <v>664</v>
       </c>
       <c r="G267">
         <v>-11.39790862267088</v>
@@ -8337,8 +8928,17 @@
       <c r="B268" t="s">
         <v>11</v>
       </c>
+      <c r="C268" t="s">
+        <v>27</v>
+      </c>
+      <c r="D268" t="s">
+        <v>72</v>
+      </c>
+      <c r="E268" t="s">
+        <v>349</v>
+      </c>
       <c r="F268" t="s">
-        <v>602</v>
+        <v>665</v>
       </c>
       <c r="G268">
         <v>-11.4044228</v>
@@ -8354,8 +8954,17 @@
       <c r="B269" t="s">
         <v>11</v>
       </c>
+      <c r="C269" t="s">
+        <v>27</v>
+      </c>
+      <c r="D269" t="s">
+        <v>72</v>
+      </c>
+      <c r="E269" t="s">
+        <v>350</v>
+      </c>
       <c r="F269" t="s">
-        <v>603</v>
+        <v>666</v>
       </c>
       <c r="G269">
         <v>-11.3902679</v>
@@ -8371,14 +8980,17 @@
       <c r="B270" t="s">
         <v>11</v>
       </c>
+      <c r="C270" t="s">
+        <v>27</v>
+      </c>
       <c r="D270" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E270" t="s">
-        <v>288</v>
+        <v>351</v>
       </c>
       <c r="F270" t="s">
-        <v>604</v>
+        <v>667</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -8388,14 +9000,17 @@
       <c r="B271" t="s">
         <v>11</v>
       </c>
+      <c r="C271" t="s">
+        <v>27</v>
+      </c>
       <c r="D271" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E271" t="s">
-        <v>289</v>
+        <v>352</v>
       </c>
       <c r="F271" t="s">
-        <v>605</v>
+        <v>668</v>
       </c>
       <c r="G271">
         <v>-11.40565087084636</v>
@@ -8411,14 +9026,17 @@
       <c r="B272" t="s">
         <v>11</v>
       </c>
+      <c r="C272" t="s">
+        <v>27</v>
+      </c>
       <c r="D272" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E272" t="s">
-        <v>290</v>
+        <v>353</v>
       </c>
       <c r="F272" t="s">
-        <v>605</v>
+        <v>668</v>
       </c>
       <c r="G272">
         <v>-11.4056579075206</v>
@@ -8434,14 +9052,17 @@
       <c r="B273" t="s">
         <v>11</v>
       </c>
+      <c r="C273" t="s">
+        <v>27</v>
+      </c>
       <c r="D273" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E273" t="s">
-        <v>291</v>
+        <v>354</v>
       </c>
       <c r="F273" t="s">
-        <v>606</v>
+        <v>669</v>
       </c>
       <c r="G273">
         <v>-11.39400456608175</v>
@@ -8457,14 +9078,17 @@
       <c r="B274" t="s">
         <v>11</v>
       </c>
+      <c r="C274" t="s">
+        <v>27</v>
+      </c>
       <c r="D274" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E274" t="s">
-        <v>292</v>
+        <v>355</v>
       </c>
       <c r="F274" t="s">
-        <v>607</v>
+        <v>670</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -8474,14 +9098,17 @@
       <c r="B275" t="s">
         <v>11</v>
       </c>
+      <c r="C275" t="s">
+        <v>27</v>
+      </c>
       <c r="D275" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E275" t="s">
-        <v>293</v>
+        <v>356</v>
       </c>
       <c r="F275" t="s">
-        <v>608</v>
+        <v>671</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -8491,14 +9118,17 @@
       <c r="B276" t="s">
         <v>11</v>
       </c>
+      <c r="C276" t="s">
+        <v>27</v>
+      </c>
       <c r="D276" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E276" t="s">
-        <v>294</v>
+        <v>357</v>
       </c>
       <c r="F276" t="s">
-        <v>609</v>
+        <v>672</v>
       </c>
       <c r="G276">
         <v>-11.40703462669001</v>
@@ -8514,14 +9144,17 @@
       <c r="B277" t="s">
         <v>11</v>
       </c>
+      <c r="C277" t="s">
+        <v>27</v>
+      </c>
       <c r="D277" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E277" t="s">
-        <v>295</v>
+        <v>358</v>
       </c>
       <c r="F277" t="s">
-        <v>610</v>
+        <v>673</v>
       </c>
       <c r="G277">
         <v>-11.3888547</v>
@@ -8537,14 +9170,17 @@
       <c r="B278" t="s">
         <v>11</v>
       </c>
+      <c r="C278" t="s">
+        <v>27</v>
+      </c>
       <c r="D278" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E278" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="F278" t="s">
-        <v>611</v>
+        <v>674</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -8554,14 +9190,17 @@
       <c r="B279" t="s">
         <v>11</v>
       </c>
+      <c r="C279" t="s">
+        <v>27</v>
+      </c>
       <c r="D279" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E279" t="s">
-        <v>297</v>
+        <v>360</v>
       </c>
       <c r="F279" t="s">
-        <v>612</v>
+        <v>675</v>
       </c>
       <c r="G279">
         <v>-11.40747624763063</v>
@@ -8577,14 +9216,17 @@
       <c r="B280" t="s">
         <v>11</v>
       </c>
+      <c r="C280" t="s">
+        <v>27</v>
+      </c>
       <c r="D280" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E280" t="s">
-        <v>298</v>
+        <v>361</v>
       </c>
       <c r="F280" t="s">
-        <v>613</v>
+        <v>676</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -8594,14 +9236,17 @@
       <c r="B281" t="s">
         <v>11</v>
       </c>
+      <c r="C281" t="s">
+        <v>27</v>
+      </c>
       <c r="D281" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E281" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="F281" t="s">
-        <v>614</v>
+        <v>677</v>
       </c>
       <c r="G281">
         <v>-11.40352975754021</v>
@@ -8617,14 +9262,17 @@
       <c r="B282" t="s">
         <v>11</v>
       </c>
+      <c r="C282" t="s">
+        <v>27</v>
+      </c>
       <c r="D282" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E282" t="s">
-        <v>300</v>
+        <v>363</v>
       </c>
       <c r="F282" t="s">
-        <v>533</v>
+        <v>596</v>
       </c>
       <c r="G282">
         <v>-11.7632851</v>
@@ -8640,14 +9288,17 @@
       <c r="B283" t="s">
         <v>11</v>
       </c>
+      <c r="C283" t="s">
+        <v>27</v>
+      </c>
       <c r="D283" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E283" t="s">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="F283" t="s">
-        <v>533</v>
+        <v>596</v>
       </c>
       <c r="G283">
         <v>-11.40882116931708</v>
@@ -8663,14 +9314,17 @@
       <c r="B284" t="s">
         <v>11</v>
       </c>
+      <c r="C284" t="s">
+        <v>27</v>
+      </c>
       <c r="D284" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E284" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="F284" t="s">
-        <v>615</v>
+        <v>678</v>
       </c>
       <c r="G284">
         <v>-11.40124567416017</v>
@@ -8686,14 +9340,17 @@
       <c r="B285" t="s">
         <v>11</v>
       </c>
+      <c r="C285" t="s">
+        <v>27</v>
+      </c>
       <c r="D285" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E285" t="s">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="F285" t="s">
-        <v>616</v>
+        <v>679</v>
       </c>
       <c r="G285">
         <v>-11.41161658570176</v>
@@ -8709,14 +9366,17 @@
       <c r="B286" t="s">
         <v>11</v>
       </c>
+      <c r="C286" t="s">
+        <v>27</v>
+      </c>
       <c r="D286" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E286" t="s">
-        <v>304</v>
+        <v>367</v>
       </c>
       <c r="F286" t="s">
-        <v>617</v>
+        <v>680</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -8726,14 +9386,17 @@
       <c r="B287" t="s">
         <v>11</v>
       </c>
+      <c r="C287" t="s">
+        <v>27</v>
+      </c>
       <c r="D287" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E287" t="s">
-        <v>305</v>
+        <v>368</v>
       </c>
       <c r="F287" t="s">
-        <v>618</v>
+        <v>681</v>
       </c>
       <c r="G287">
         <v>-11.41553451680188</v>
@@ -8749,14 +9412,17 @@
       <c r="B288" t="s">
         <v>11</v>
       </c>
+      <c r="C288" t="s">
+        <v>27</v>
+      </c>
       <c r="D288" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E288" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="F288" t="s">
-        <v>619</v>
+        <v>682</v>
       </c>
       <c r="G288">
         <v>-11.4020466</v>
@@ -8772,14 +9438,17 @@
       <c r="B289" t="s">
         <v>11</v>
       </c>
+      <c r="C289" t="s">
+        <v>27</v>
+      </c>
       <c r="D289" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E289" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="F289" t="s">
-        <v>620</v>
+        <v>683</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -8789,14 +9458,17 @@
       <c r="B290" t="s">
         <v>11</v>
       </c>
+      <c r="C290" t="s">
+        <v>27</v>
+      </c>
       <c r="D290" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E290" t="s">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="F290" t="s">
-        <v>621</v>
+        <v>684</v>
       </c>
       <c r="G290">
         <v>-11.44765</v>
@@ -8812,14 +9484,17 @@
       <c r="B291" t="s">
         <v>11</v>
       </c>
+      <c r="C291" t="s">
+        <v>27</v>
+      </c>
       <c r="D291" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E291" t="s">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="F291" t="s">
-        <v>622</v>
+        <v>685</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -8829,14 +9504,17 @@
       <c r="B292" t="s">
         <v>11</v>
       </c>
+      <c r="C292" t="s">
+        <v>27</v>
+      </c>
       <c r="D292" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E292" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="F292" t="s">
-        <v>623</v>
+        <v>686</v>
       </c>
       <c r="G292">
         <v>-11.4212636</v>
@@ -8852,14 +9530,17 @@
       <c r="B293" t="s">
         <v>11</v>
       </c>
+      <c r="C293" t="s">
+        <v>27</v>
+      </c>
       <c r="D293" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E293" t="s">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="F293" t="s">
-        <v>624</v>
+        <v>687</v>
       </c>
       <c r="G293">
         <v>-11.44618350414512</v>
@@ -8875,14 +9556,17 @@
       <c r="B294" t="s">
         <v>11</v>
       </c>
+      <c r="C294" t="s">
+        <v>27</v>
+      </c>
       <c r="D294" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E294" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="F294" t="s">
-        <v>625</v>
+        <v>688</v>
       </c>
       <c r="G294">
         <v>-11.44038065465517</v>
@@ -8898,14 +9582,17 @@
       <c r="B295" t="s">
         <v>11</v>
       </c>
+      <c r="C295" t="s">
+        <v>27</v>
+      </c>
       <c r="D295" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E295" t="s">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="F295" t="s">
-        <v>626</v>
+        <v>689</v>
       </c>
       <c r="G295">
         <v>-11.4242569</v>
@@ -8921,14 +9608,17 @@
       <c r="B296" t="s">
         <v>11</v>
       </c>
+      <c r="C296" t="s">
+        <v>27</v>
+      </c>
       <c r="D296" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E296" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="F296" t="s">
-        <v>605</v>
+        <v>668</v>
       </c>
       <c r="G296">
         <v>-11.40565087084636</v>
@@ -8944,14 +9634,17 @@
       <c r="B297" t="s">
         <v>11</v>
       </c>
+      <c r="C297" t="s">
+        <v>27</v>
+      </c>
       <c r="D297" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E297" t="s">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="F297" t="s">
-        <v>605</v>
+        <v>668</v>
       </c>
       <c r="G297">
         <v>-11.4056579075206</v>
@@ -8967,14 +9660,17 @@
       <c r="B298" t="s">
         <v>11</v>
       </c>
+      <c r="C298" t="s">
+        <v>27</v>
+      </c>
       <c r="D298" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E298" t="s">
-        <v>316</v>
+        <v>379</v>
       </c>
       <c r="F298" t="s">
-        <v>627</v>
+        <v>690</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8984,14 +9680,17 @@
       <c r="B299" t="s">
         <v>11</v>
       </c>
+      <c r="C299" t="s">
+        <v>27</v>
+      </c>
       <c r="D299" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E299" t="s">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="F299" t="s">
-        <v>628</v>
+        <v>691</v>
       </c>
       <c r="G299">
         <v>-11.4796887</v>
@@ -9007,14 +9706,17 @@
       <c r="B300" t="s">
         <v>11</v>
       </c>
+      <c r="C300" t="s">
+        <v>27</v>
+      </c>
       <c r="D300" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E300" t="s">
-        <v>318</v>
+        <v>381</v>
       </c>
       <c r="F300" t="s">
-        <v>629</v>
+        <v>692</v>
       </c>
       <c r="G300">
         <v>-11.4675610308968</v>
@@ -9030,14 +9732,17 @@
       <c r="B301" t="s">
         <v>11</v>
       </c>
+      <c r="C301" t="s">
+        <v>27</v>
+      </c>
       <c r="D301" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E301" t="s">
-        <v>319</v>
+        <v>382</v>
       </c>
       <c r="F301" t="s">
-        <v>630</v>
+        <v>693</v>
       </c>
       <c r="G301">
         <v>-11.4669826</v>
@@ -9053,14 +9758,17 @@
       <c r="B302" t="s">
         <v>11</v>
       </c>
+      <c r="C302" t="s">
+        <v>27</v>
+      </c>
       <c r="D302" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E302" t="s">
-        <v>320</v>
+        <v>383</v>
       </c>
       <c r="F302" t="s">
-        <v>631</v>
+        <v>694</v>
       </c>
       <c r="G302">
         <v>-11.46917108118241</v>
@@ -9076,14 +9784,17 @@
       <c r="B303" t="s">
         <v>11</v>
       </c>
+      <c r="C303" t="s">
+        <v>27</v>
+      </c>
       <c r="D303" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E303" t="s">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="F303" t="s">
-        <v>632</v>
+        <v>695</v>
       </c>
       <c r="G303">
         <v>-11.47548241525642</v>
@@ -9099,14 +9810,17 @@
       <c r="B304" t="s">
         <v>11</v>
       </c>
+      <c r="C304" t="s">
+        <v>27</v>
+      </c>
       <c r="D304" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E304" t="s">
-        <v>322</v>
+        <v>385</v>
       </c>
       <c r="F304" t="s">
-        <v>633</v>
+        <v>696</v>
       </c>
       <c r="G304">
         <v>-11.48742364099441</v>
@@ -9122,14 +9836,17 @@
       <c r="B305" t="s">
         <v>11</v>
       </c>
+      <c r="C305" t="s">
+        <v>27</v>
+      </c>
       <c r="D305" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E305" t="s">
-        <v>323</v>
+        <v>386</v>
       </c>
       <c r="F305" t="s">
-        <v>634</v>
+        <v>697</v>
       </c>
       <c r="G305">
         <v>-11.4909321719639</v>
@@ -9145,14 +9862,17 @@
       <c r="B306" t="s">
         <v>11</v>
       </c>
+      <c r="C306" t="s">
+        <v>27</v>
+      </c>
       <c r="D306" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E306" t="s">
-        <v>324</v>
+        <v>387</v>
       </c>
       <c r="F306" t="s">
-        <v>635</v>
+        <v>698</v>
       </c>
       <c r="G306">
         <v>-11.47145133531327</v>
@@ -9169,16 +9889,16 @@
         <v>11</v>
       </c>
       <c r="C307" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D307" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E307" t="s">
-        <v>325</v>
+        <v>388</v>
       </c>
       <c r="F307" t="s">
-        <v>636</v>
+        <v>699</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -9189,16 +9909,16 @@
         <v>11</v>
       </c>
       <c r="C308" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D308" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E308" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="F308" t="s">
-        <v>637</v>
+        <v>700</v>
       </c>
       <c r="G308">
         <v>-11.5664502</v>
@@ -9215,16 +9935,16 @@
         <v>11</v>
       </c>
       <c r="C309" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D309" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E309" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="F309" t="s">
-        <v>638</v>
+        <v>701</v>
       </c>
       <c r="G309">
         <v>-11.55689073602729</v>
@@ -9241,16 +9961,16 @@
         <v>11</v>
       </c>
       <c r="C310" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D310" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E310" t="s">
-        <v>328</v>
+        <v>391</v>
       </c>
       <c r="F310" t="s">
-        <v>639</v>
+        <v>702</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -9261,16 +9981,16 @@
         <v>11</v>
       </c>
       <c r="C311" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D311" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E311" t="s">
-        <v>329</v>
+        <v>392</v>
       </c>
       <c r="F311" t="s">
-        <v>640</v>
+        <v>703</v>
       </c>
       <c r="G311">
         <v>-11.588576</v>
@@ -9287,16 +10007,16 @@
         <v>11</v>
       </c>
       <c r="C312" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D312" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E312" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="F312" t="s">
-        <v>641</v>
+        <v>704</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -9307,16 +10027,16 @@
         <v>11</v>
       </c>
       <c r="C313" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D313" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E313" t="s">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="F313" t="s">
-        <v>642</v>
+        <v>705</v>
       </c>
       <c r="G313">
         <v>-11.5600257</v>
@@ -9333,16 +10053,16 @@
         <v>11</v>
       </c>
       <c r="C314" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D314" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E314" t="s">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="F314" t="s">
-        <v>643</v>
+        <v>706</v>
       </c>
       <c r="G314">
         <v>-11.5772493</v>
@@ -9359,16 +10079,16 @@
         <v>11</v>
       </c>
       <c r="C315" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D315" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E315" t="s">
-        <v>333</v>
+        <v>396</v>
       </c>
       <c r="F315" t="s">
-        <v>644</v>
+        <v>707</v>
       </c>
       <c r="G315">
         <v>-11.55527994994988</v>
@@ -9385,16 +10105,16 @@
         <v>11</v>
       </c>
       <c r="C316" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D316" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E316" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="F316" t="s">
-        <v>645</v>
+        <v>708</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -9405,16 +10125,16 @@
         <v>11</v>
       </c>
       <c r="C317" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D317" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E317" t="s">
-        <v>335</v>
+        <v>398</v>
       </c>
       <c r="F317" t="s">
-        <v>646</v>
+        <v>709</v>
       </c>
       <c r="G317">
         <v>-11.61498594113464</v>
@@ -9431,16 +10151,16 @@
         <v>11</v>
       </c>
       <c r="C318" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D318" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E318" t="s">
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="F318" t="s">
-        <v>647</v>
+        <v>710</v>
       </c>
       <c r="G318">
         <v>-11.61070176560084</v>
@@ -9457,16 +10177,16 @@
         <v>11</v>
       </c>
       <c r="C319" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D319" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E319" t="s">
-        <v>337</v>
+        <v>400</v>
       </c>
       <c r="F319" t="s">
-        <v>648</v>
+        <v>711</v>
       </c>
       <c r="G319">
         <v>-11.61408863684719</v>
@@ -9483,16 +10203,16 @@
         <v>11</v>
       </c>
       <c r="C320" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D320" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E320" t="s">
-        <v>338</v>
+        <v>401</v>
       </c>
       <c r="F320" t="s">
-        <v>649</v>
+        <v>712</v>
       </c>
       <c r="G320">
         <v>-11.62985962546771</v>
@@ -9509,16 +10229,16 @@
         <v>11</v>
       </c>
       <c r="C321" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D321" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E321" t="s">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="F321" t="s">
-        <v>650</v>
+        <v>713</v>
       </c>
       <c r="G321">
         <v>-11.61454045570641</v>
@@ -9535,16 +10255,16 @@
         <v>11</v>
       </c>
       <c r="C322" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D322" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E322" t="s">
-        <v>340</v>
+        <v>403</v>
       </c>
       <c r="F322" t="s">
-        <v>651</v>
+        <v>714</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -9555,16 +10275,16 @@
         <v>11</v>
       </c>
       <c r="C323" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D323" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E323" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="F323" t="s">
-        <v>652</v>
+        <v>715</v>
       </c>
       <c r="G323">
         <v>-11.68426517737763</v>
@@ -9581,16 +10301,16 @@
         <v>11</v>
       </c>
       <c r="C324" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D324" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E324" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="F324" t="s">
-        <v>653</v>
+        <v>716</v>
       </c>
       <c r="G324">
         <v>-11.67513716887363</v>
@@ -9607,16 +10327,16 @@
         <v>11</v>
       </c>
       <c r="C325" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D325" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E325" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
       <c r="F325" t="s">
-        <v>654</v>
+        <v>717</v>
       </c>
       <c r="G325">
         <v>-11.66092453146139</v>
@@ -9633,16 +10353,16 @@
         <v>11</v>
       </c>
       <c r="C326" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D326" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E326" t="s">
-        <v>344</v>
+        <v>407</v>
       </c>
       <c r="F326" t="s">
-        <v>655</v>
+        <v>718</v>
       </c>
       <c r="G326">
         <v>-11.67489295143956</v>
@@ -9659,16 +10379,16 @@
         <v>11</v>
       </c>
       <c r="C327" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D327" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E327" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="F327" t="s">
-        <v>656</v>
+        <v>719</v>
       </c>
       <c r="G327">
         <v>-11.68235042563022</v>
@@ -9685,16 +10405,16 @@
         <v>11</v>
       </c>
       <c r="C328" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D328" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E328" t="s">
-        <v>346</v>
+        <v>409</v>
       </c>
       <c r="F328" t="s">
-        <v>657</v>
+        <v>720</v>
       </c>
       <c r="G328">
         <v>-11.6712913</v>
@@ -9711,16 +10431,16 @@
         <v>11</v>
       </c>
       <c r="C329" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D329" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E329" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="F329" t="s">
-        <v>658</v>
+        <v>721</v>
       </c>
       <c r="G329">
         <v>-11.67587607348723</v>
@@ -9737,16 +10457,16 @@
         <v>11</v>
       </c>
       <c r="C330" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D330" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E330" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="F330" t="s">
-        <v>659</v>
+        <v>722</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9757,16 +10477,16 @@
         <v>11</v>
       </c>
       <c r="C331" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D331" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E331" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="F331" t="s">
-        <v>660</v>
+        <v>723</v>
       </c>
       <c r="G331">
         <v>-11.6428324</v>
@@ -9783,16 +10503,16 @@
         <v>11</v>
       </c>
       <c r="C332" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D332" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E332" t="s">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="F332" t="s">
-        <v>446</v>
+        <v>509</v>
       </c>
       <c r="G332">
         <v>-11.64868566292302</v>
@@ -9809,16 +10529,16 @@
         <v>11</v>
       </c>
       <c r="C333" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D333" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E333" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F333" t="s">
-        <v>661</v>
+        <v>724</v>
       </c>
       <c r="G333">
         <v>-11.65109434513936</v>
@@ -9835,16 +10555,16 @@
         <v>11</v>
       </c>
       <c r="C334" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D334" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E334" t="s">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="F334" t="s">
-        <v>662</v>
+        <v>725</v>
       </c>
       <c r="G334">
         <v>-11.6513186</v>
@@ -9861,16 +10581,16 @@
         <v>11</v>
       </c>
       <c r="C335" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D335" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E335" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="F335" t="s">
-        <v>663</v>
+        <v>726</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -9881,16 +10601,16 @@
         <v>11</v>
       </c>
       <c r="C336" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D336" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E336" t="s">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="F336" t="s">
-        <v>664</v>
+        <v>727</v>
       </c>
       <c r="G336">
         <v>-11.66400689532476</v>
@@ -9907,16 +10627,16 @@
         <v>11</v>
       </c>
       <c r="C337" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D337" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E337" t="s">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="F337" t="s">
-        <v>451</v>
+        <v>514</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -9927,16 +10647,16 @@
         <v>11</v>
       </c>
       <c r="C338" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D338" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E338" t="s">
-        <v>356</v>
+        <v>419</v>
       </c>
       <c r="F338" t="s">
-        <v>451</v>
+        <v>514</v>
       </c>
       <c r="G338">
         <v>-12.20224155888374</v>
@@ -9953,16 +10673,16 @@
         <v>11</v>
       </c>
       <c r="C339" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D339" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E339" t="s">
-        <v>357</v>
+        <v>420</v>
       </c>
       <c r="F339" t="s">
-        <v>665</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
